--- a/output/蒼穹のレガリア II_align-on_行程グループ.xlsx
+++ b/output/蒼穹のレガリア II_align-on_行程グループ.xlsx
@@ -2543,7 +2543,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 03:12</t>
+          <t>2026-09-04 23:00</t>
         </is>
       </c>
     </row>
@@ -70852,7 +70852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -70909,7 +70909,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>2026-09-04 03:12:21</t>
+          <t>2026-09-04 23:00:51</t>
         </is>
       </c>
     </row>
@@ -71020,567 +71020,358 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>カーブ復元</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>月内均等</t>
-        </is>
+          <t>区間弾力性</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>カーブ解像度</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>100</v>
+          <t>カーブ復元</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>月内均等</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>人月換算係数</t>
+          <t>カーブ解像度</t>
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>段階予測のマイルストーン</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>すべて</t>
-        </is>
+          <t>人月換算係数</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>実装範囲</t>
+          <t>見積もりを使う</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>実装順序 1〜2(素朴版 + マイルストーン位置合わせ) + 見積もりによる総量指定</t>
+          <t>ON</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>未使用パラメータ</t>
+          <t>除外する行程グループ</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>k=3.0, タグ重み係数=0.5 (実装順序 3・4 で使用予定)</t>
+          <t>(なし)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>予測対象</t>
+          <t>立ち上がり上限</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>PJ-2026-K  蒼穹のレガリア II</t>
+          <t>使用しない</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>学習案件数</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="n">
-        <v>10</v>
+          <t>立ち上がり上限の適用範囲</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>段階予測のみ</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>総量の根拠</t>
+          <t>段階予測の動作</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>契約人月 + 学習比率</t>
+          <t>自動</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>予測した行程グループ</t>
+          <t>段階予測の残工数</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>企画・プリプロ, ゲームデザイン・シナリオ, プログラム, アート, サウンド, QA・デバッグ, PM・運営</t>
+          <t>固定</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>除外した行程グループ</t>
+          <t>段階予測のマイルストーン</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>(なし)</t>
+          <t>すべて</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>段階予測</t>
+          <t>検証</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>(出力なし)</t>
+          <t>ON</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>立ち上がり上限</t>
+          <t>カーブ復元の比較</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>使用しない</t>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>出力先フォルダ</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>/home/user/Man-hour-forecasting/output</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>■ 人月換算</t>
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>実装範囲</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>実装順序 1〜2(素朴版 + マイルストーン位置合わせ) + 見積もりによる総量指定</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>換算係数</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>時間 / 人月</t>
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>未使用パラメータ</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>k=3.0, タグ重み係数=0.5 (実装順序 3・4 で使用予定)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>人月の定義は組織によって揺れる。この係数を明記しないまま数字が独り歩きすると議論が噛み合わなくなる(設計書 4-3)。</t>
-        </is>
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>予測対象</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>PJ-2026-K  蒼穹のレガリア II</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>学習案件数</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>■ 学習に使用した案件と重み</t>
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>総量の根拠</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>契約人月 + 学習比率</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>第1版(素朴版+位置合わせ)では全案件の重みを 1.0 で固定している。種別・タグによる重み付けは実装順序 3・4 で導入する。</t>
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>予測した行程グループ</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>企画・プリプロ, ゲームデザイン・シナリオ, プログラム, アート, サウンド, QA・デバッグ, PM・運営</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>案件ID</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>重み</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>契約人月</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>実績人月</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>乖離率(%)</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>期間(月)</t>
-        </is>
-      </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>マイルストーン数</t>
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>除外した行程グループ</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>(なし)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PJ-2019-A</t>
+          <t>段階予測</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>蒼穹のレガリア</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>新規タイトル開発</t>
-        </is>
-      </c>
-      <c r="D37" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="12" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F37" s="12" t="n">
-        <v>2372.3</v>
-      </c>
-      <c r="G37" s="10" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="H37" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="I37" s="10" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>PJ-2020-B</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>ブレイブフロンティア外伝(後半集中)</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>大型アップデート</t>
-        </is>
-      </c>
-      <c r="D38" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="12" t="n">
-        <v>620</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>625.1</v>
-      </c>
-      <c r="G38" s="10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H38" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="I38" s="10" t="n">
-        <v>3</v>
+          <t>(出力なし)</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>PJ-2020-C</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>クロノスギア(二山)</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>新規タイトル開発</t>
-        </is>
-      </c>
-      <c r="D39" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="12" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>1806.5</v>
-      </c>
-      <c r="G39" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H39" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="I39" s="10" t="n">
-        <v>4</v>
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>■ 人月換算</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>PJ-2021-D</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>蒼穹のレガリア HD Edition(前倒し)</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>移植・リマスター</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>520</v>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>518.2</v>
-      </c>
-      <c r="G40" s="10" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H40" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="I40" s="10" t="n">
-        <v>3</v>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>換算係数</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>時間 / 人月</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>PJ-2021-E</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>シャドウヴェイル</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>新規タイトル開発</t>
-        </is>
-      </c>
-      <c r="D41" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="12" t="n">
-        <v>2950</v>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>3013.4</v>
-      </c>
-      <c r="G41" s="10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H41" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="I41" s="10" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>PJ-2022-F</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>ネオンハーツ Season2</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>大型アップデート</t>
-        </is>
-      </c>
-      <c r="D42" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>880</v>
-      </c>
-      <c r="F42" s="12" t="n">
-        <v>881.8</v>
-      </c>
-      <c r="G42" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H42" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="I42" s="10" t="n">
-        <v>3</v>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>人月の定義は組織によって揺れる。この係数を明記しないまま数字が独り歩きすると議論が噛み合わなくなる(設計書 4-3)。</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>PJ-2022-G</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>ギルドマスターズ(前倒し)</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>新規タイトル開発</t>
-        </is>
-      </c>
-      <c r="D43" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="12" t="n">
-        <v>1450</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>1461</v>
-      </c>
-      <c r="G43" s="10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H43" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="I43" s="10" t="n">
-        <v>4</v>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>■ 学習に使用した案件と重み</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>PJ-2023-H</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>クロノスギア:蒼き遺産</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>大型アップデート</t>
-        </is>
-      </c>
-      <c r="D44" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="12" t="n">
-        <v>1100</v>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>1104.9</v>
-      </c>
-      <c r="G44" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H44" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="I44" s="10" t="n">
-        <v>3</v>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>第1版(素朴版+位置合わせ)では全案件の重みを 1.0 で固定している。種別・タグによる重み付けは実装順序 3・4 で導入する。</t>
+        </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>PJ-2023-I</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>ブレイブフロンティア Remaster</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>移植・リマスター</t>
-        </is>
-      </c>
-      <c r="D45" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="12" t="n">
-        <v>700</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>709.7</v>
-      </c>
-      <c r="G45" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H45" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="I45" s="10" t="n">
-        <v>3</v>
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>案件ID</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>重み</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>契約人月</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>実績人月</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>乖離率(%)</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>期間(月)</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>マイルストーン数</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>PJ-2024-J</t>
+          <t>PJ-2019-A</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>オーヴァーロード・サーガ(後半集中)</t>
+          <t>蒼穹のレガリア</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -71592,797 +71383,1112 @@
         <v>1</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>2162.6</v>
+        <v>2372.3</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>-1.7</v>
+        <v>-1.2</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>4</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>PJ-2020-B</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>ブレイブフロンティア外伝(後半集中)</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>大型アップデート</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>620</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>625.1</v>
+      </c>
+      <c r="G47" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H47" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="I47" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>■ 案件別 × 行程グループ 実績工数(人月)</t>
-        </is>
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>PJ-2020-C</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>クロノスギア(二山)</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>新規タイトル開発</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>1806.5</v>
+      </c>
+      <c r="G48" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>予測と同じ集計(phase_map に載る行程・契約期間内)での実績合計。0 はその案件がその業務を行っていないことを示す。最下行は全案件の合計で、その構成比が学習値そのものではない点に注意(学習は案件ごとの構成比を平均するため、規模の大きい案件に引っ張られない)。</t>
-        </is>
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>PJ-2021-D</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>蒼穹のレガリア HD Edition(前倒し)</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>移植・リマスター</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>520</v>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>518.2</v>
+      </c>
+      <c r="G49" s="10" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I49" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>PJ-2021-E</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>シャドウヴェイル</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>新規タイトル開発</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>2950</v>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>3013.4</v>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H50" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="I50" s="10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>案件ID</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>期間(月)</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>企画・プリプロ</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>ゲームデザイン・シナリオ</t>
-        </is>
-      </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>プログラム</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>アート</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="inlineStr">
-        <is>
-          <t>サウンド</t>
-        </is>
-      </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>QA・デバッグ</t>
-        </is>
-      </c>
-      <c r="J51" s="8" t="inlineStr">
-        <is>
-          <t>PM・運営</t>
-        </is>
-      </c>
-      <c r="K51" s="8" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>PJ-2022-F</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>ネオンハーツ Season2</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>大型アップデート</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>880</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>881.8</v>
+      </c>
+      <c r="G51" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H51" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="I51" s="10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>PJ-2019-A</t>
+          <t>PJ-2022-G</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>蒼穹のレガリア</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="D52" s="19" t="n">
-        <v>185</v>
-      </c>
-      <c r="E52" s="19" t="n">
-        <v>297.4</v>
-      </c>
-      <c r="F52" s="19" t="n">
-        <v>589.6</v>
-      </c>
-      <c r="G52" s="19" t="n">
-        <v>772.4</v>
-      </c>
-      <c r="H52" s="19" t="n">
-        <v>119.1</v>
-      </c>
-      <c r="I52" s="19" t="n">
-        <v>272.4</v>
-      </c>
-      <c r="J52" s="19" t="n">
-        <v>136.4</v>
-      </c>
-      <c r="K52" s="19" t="n">
-        <v>2372.3</v>
+          <t>ギルドマスターズ(前倒し)</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>新規タイトル開発</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>1461</v>
+      </c>
+      <c r="G52" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H52" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I52" s="10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PJ-2020-B</t>
+          <t>PJ-2023-H</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>ブレイブフロンティア外伝(後半集中)</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="D53" s="19" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="E53" s="19" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="F53" s="19" t="n">
-        <v>145.7</v>
-      </c>
-      <c r="G53" s="19" t="n">
-        <v>202.1</v>
-      </c>
-      <c r="H53" s="19" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="I53" s="19" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="J53" s="19" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="K53" s="19" t="n">
-        <v>625.1</v>
+          <t>クロノスギア:蒼き遺産</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>大型アップデート</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>1104.9</v>
+      </c>
+      <c r="G53" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="I53" s="10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>PJ-2020-C</t>
+          <t>PJ-2023-I</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>クロノスギア(二山)</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="D54" s="19" t="n">
-        <v>141.4</v>
-      </c>
-      <c r="E54" s="19" t="n">
-        <v>217.4</v>
-      </c>
-      <c r="F54" s="19" t="n">
-        <v>502.4</v>
-      </c>
-      <c r="G54" s="19" t="n">
-        <v>524.6</v>
-      </c>
-      <c r="H54" s="19" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="I54" s="19" t="n">
-        <v>225.2</v>
-      </c>
-      <c r="J54" s="19" t="n">
-        <v>108.2</v>
-      </c>
-      <c r="K54" s="19" t="n">
-        <v>1806.5</v>
+          <t>ブレイブフロンティア Remaster</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>移植・リマスター</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>700</v>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>709.7</v>
+      </c>
+      <c r="G54" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H54" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="I54" s="10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PJ-2021-D</t>
+          <t>PJ-2024-J</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>蒼穹のレガリア HD Edition(前倒し)</t>
-        </is>
-      </c>
-      <c r="C55" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="D55" s="19" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="E55" s="19" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="F55" s="19" t="n">
-        <v>211.1</v>
-      </c>
-      <c r="G55" s="19" t="n">
-        <v>127.2</v>
-      </c>
-      <c r="H55" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="I55" s="19" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="J55" s="19" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="K55" s="19" t="n">
-        <v>518.2</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>PJ-2021-E</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>シャドウヴェイル</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="D56" s="19" t="n">
-        <v>251</v>
-      </c>
-      <c r="E56" s="19" t="n">
-        <v>373</v>
-      </c>
-      <c r="F56" s="19" t="n">
-        <v>795.5</v>
-      </c>
-      <c r="G56" s="19" t="n">
-        <v>930.9</v>
-      </c>
-      <c r="H56" s="19" t="n">
-        <v>147.4</v>
-      </c>
-      <c r="I56" s="19" t="n">
-        <v>346.7</v>
-      </c>
-      <c r="J56" s="19" t="n">
-        <v>168.9</v>
-      </c>
-      <c r="K56" s="19" t="n">
-        <v>3013.4</v>
+          <t>オーヴァーロード・サーガ(後半集中)</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>新規タイトル開発</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>2162.6</v>
+      </c>
+      <c r="G55" s="10" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="H55" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>PJ-2022-F</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>ネオンハーツ Season2</t>
-        </is>
-      </c>
-      <c r="C57" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="D57" s="19" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="E57" s="19" t="n">
-        <v>129.1</v>
-      </c>
-      <c r="F57" s="19" t="n">
-        <v>204.3</v>
-      </c>
-      <c r="G57" s="19" t="n">
-        <v>286.5</v>
-      </c>
-      <c r="H57" s="19" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="I57" s="19" t="n">
-        <v>124.6</v>
-      </c>
-      <c r="J57" s="19" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="K57" s="19" t="n">
-        <v>881.8</v>
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>■ 案件別 × 行程グループ 実績工数(人月)</t>
+        </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>PJ-2022-G</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>ギルドマスターズ(前倒し)</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="D58" s="19" t="n">
-        <v>123.2</v>
-      </c>
-      <c r="E58" s="19" t="n">
-        <v>170</v>
-      </c>
-      <c r="F58" s="19" t="n">
-        <v>392.3</v>
-      </c>
-      <c r="G58" s="19" t="n">
-        <v>446</v>
-      </c>
-      <c r="H58" s="19" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="I58" s="19" t="n">
-        <v>171.6</v>
-      </c>
-      <c r="J58" s="19" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="K58" s="19" t="n">
-        <v>1461</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>PJ-2023-H</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>クロノスギア:蒼き遺産</t>
-        </is>
-      </c>
-      <c r="C59" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="D59" s="19" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="E59" s="19" t="n">
-        <v>155.3</v>
-      </c>
-      <c r="F59" s="19" t="n">
-        <v>260.3</v>
-      </c>
-      <c r="G59" s="19" t="n">
-        <v>371</v>
-      </c>
-      <c r="H59" s="19" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="I59" s="19" t="n">
-        <v>150.1</v>
-      </c>
-      <c r="J59" s="19" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="K59" s="19" t="n">
-        <v>1104.9</v>
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>予測と同じ集計(phase_map に載る行程・契約期間内)での実績合計。0 はその案件がその業務を行っていないことを示す。最下行は全案件の合計で、その構成比が学習値そのものではない点に注意(学習は案件ごとの構成比を平均するため、規模の大きい案件に引っ張られない)。</t>
+        </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>PJ-2023-I</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>ブレイブフロンティア Remaster</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="D60" s="19" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E60" s="19" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="F60" s="19" t="n">
-        <v>308.5</v>
-      </c>
-      <c r="G60" s="19" t="n">
-        <v>171.1</v>
-      </c>
-      <c r="H60" s="19" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I60" s="19" t="n">
-        <v>106.1</v>
-      </c>
-      <c r="J60" s="19" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="K60" s="19" t="n">
-        <v>709.7</v>
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>案件ID</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>期間(月)</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>企画・プリプロ</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>ゲームデザイン・シナリオ</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>プログラム</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>アート</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>サウンド</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>QA・デバッグ</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>PM・運営</t>
+        </is>
+      </c>
+      <c r="K60" s="8" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PJ-2024-J</t>
+          <t>PJ-2019-A</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>オーヴァーロード・サーガ(後半集中)</t>
+          <t>蒼穹のレガリア</t>
         </is>
       </c>
       <c r="C61" s="10" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D61" s="19" t="n">
-        <v>153.8</v>
+        <v>185</v>
       </c>
       <c r="E61" s="19" t="n">
-        <v>254</v>
+        <v>297.4</v>
       </c>
       <c r="F61" s="19" t="n">
-        <v>600.1</v>
+        <v>589.6</v>
       </c>
       <c r="G61" s="19" t="n">
-        <v>658.4</v>
+        <v>772.4</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>122.6</v>
+        <v>119.1</v>
       </c>
       <c r="I61" s="19" t="n">
-        <v>234.8</v>
+        <v>272.4</v>
       </c>
       <c r="J61" s="19" t="n">
-        <v>138.9</v>
+        <v>136.4</v>
       </c>
       <c r="K61" s="19" t="n">
-        <v>2162.6</v>
+        <v>2372.3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B62" s="10" t="inlineStr"/>
-      <c r="C62" s="10" t="n"/>
+          <t>PJ-2020-B</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>ブレイブフロンティア外伝(後半集中)</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="n">
+        <v>14</v>
+      </c>
       <c r="D62" s="19" t="n">
-        <v>1056.6</v>
+        <v>40.2</v>
       </c>
       <c r="E62" s="19" t="n">
-        <v>1740.3</v>
+        <v>85.5</v>
       </c>
       <c r="F62" s="19" t="n">
-        <v>4009.8</v>
+        <v>145.7</v>
       </c>
       <c r="G62" s="19" t="n">
-        <v>4490.2</v>
+        <v>202.1</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>686.6</v>
+        <v>25.6</v>
       </c>
       <c r="I62" s="19" t="n">
-        <v>1812.3</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="J62" s="19" t="n">
-        <v>860.1</v>
+        <v>38.5</v>
       </c>
       <c r="K62" s="19" t="n">
-        <v>14655.5</v>
+        <v>625.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>構成比</t>
+          <t>PJ-2020-C</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>(全案件の単純合計)</t>
-        </is>
-      </c>
-      <c r="C63" s="10" t="n"/>
-      <c r="D63" s="17" t="n">
-        <v>0.0721</v>
-      </c>
-      <c r="E63" s="17" t="n">
-        <v>0.1187</v>
-      </c>
-      <c r="F63" s="17" t="n">
-        <v>0.2736</v>
-      </c>
-      <c r="G63" s="17" t="n">
-        <v>0.3064</v>
-      </c>
-      <c r="H63" s="17" t="n">
-        <v>0.0468</v>
-      </c>
-      <c r="I63" s="17" t="n">
-        <v>0.1237</v>
-      </c>
-      <c r="J63" s="17" t="n">
-        <v>0.0587</v>
-      </c>
-      <c r="K63" s="17" t="n">
-        <v>1</v>
+          <t>クロノスギア(二山)</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="D63" s="19" t="n">
+        <v>141.4</v>
+      </c>
+      <c r="E63" s="19" t="n">
+        <v>217.4</v>
+      </c>
+      <c r="F63" s="19" t="n">
+        <v>502.4</v>
+      </c>
+      <c r="G63" s="19" t="n">
+        <v>524.6</v>
+      </c>
+      <c r="H63" s="19" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="I63" s="19" t="n">
+        <v>225.2</v>
+      </c>
+      <c r="J63" s="19" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="K63" s="19" t="n">
+        <v>1806.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>PJ-2021-D</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>蒼穹のレガリア HD Edition(前倒し)</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="D64" s="19" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="E64" s="19" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F64" s="19" t="n">
+        <v>211.1</v>
+      </c>
+      <c r="G64" s="19" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="H64" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="I64" s="19" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="J64" s="19" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="K64" s="19" t="n">
+        <v>518.2</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>■ マイルストーン位置分布(学習値)</t>
-        </is>
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>PJ-2021-E</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>シャドウヴェイル</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="D65" s="19" t="n">
+        <v>251</v>
+      </c>
+      <c r="E65" s="19" t="n">
+        <v>373</v>
+      </c>
+      <c r="F65" s="19" t="n">
+        <v>795.5</v>
+      </c>
+      <c r="G65" s="19" t="n">
+        <v>930.9</v>
+      </c>
+      <c r="H65" s="19" t="n">
+        <v>147.4</v>
+      </c>
+      <c r="I65" s="19" t="n">
+        <v>346.7</v>
+      </c>
+      <c r="J65" s="19" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="K65" s="19" t="n">
+        <v>3013.4</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>マイルストーン名</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>平均位置</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>標準偏差</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>件数</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>背骨</t>
-        </is>
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>PJ-2022-F</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>ネオンハーツ Season2</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="D66" s="19" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="E66" s="19" t="n">
+        <v>129.1</v>
+      </c>
+      <c r="F66" s="19" t="n">
+        <v>204.3</v>
+      </c>
+      <c r="G66" s="19" t="n">
+        <v>286.5</v>
+      </c>
+      <c r="H66" s="19" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="I66" s="19" t="n">
+        <v>124.6</v>
+      </c>
+      <c r="J66" s="19" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="K66" s="19" t="n">
+        <v>881.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>プロトタイプ</t>
-        </is>
-      </c>
-      <c r="B67" s="21" t="n">
-        <v>0.2277301327110109</v>
-      </c>
-      <c r="C67" s="21" t="n">
-        <v>0.03189012393515308</v>
-      </c>
-      <c r="D67" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E67" s="10" t="inlineStr"/>
+          <t>PJ-2022-G</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>ギルドマスターズ(前倒し)</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="D67" s="19" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="E67" s="19" t="n">
+        <v>170</v>
+      </c>
+      <c r="F67" s="19" t="n">
+        <v>392.3</v>
+      </c>
+      <c r="G67" s="19" t="n">
+        <v>446</v>
+      </c>
+      <c r="H67" s="19" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="I67" s="19" t="n">
+        <v>171.6</v>
+      </c>
+      <c r="J67" s="19" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="K67" s="19" t="n">
+        <v>1461</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>α版</t>
-        </is>
-      </c>
-      <c r="B68" s="21" t="n">
-        <v>0.4968946897102826</v>
-      </c>
-      <c r="C68" s="21" t="n">
-        <v>0.05787603873596738</v>
-      </c>
-      <c r="D68" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
+          <t>PJ-2023-H</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>クロノスギア:蒼き遺産</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D68" s="19" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="E68" s="19" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="F68" s="19" t="n">
+        <v>260.3</v>
+      </c>
+      <c r="G68" s="19" t="n">
+        <v>371</v>
+      </c>
+      <c r="H68" s="19" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="I68" s="19" t="n">
+        <v>150.1</v>
+      </c>
+      <c r="J68" s="19" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="K68" s="19" t="n">
+        <v>1104.9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>β版</t>
-        </is>
-      </c>
-      <c r="B69" s="21" t="n">
-        <v>0.7378800534841294</v>
-      </c>
-      <c r="C69" s="21" t="n">
-        <v>0.05000354072467814</v>
-      </c>
-      <c r="D69" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E69" s="10" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
+          <t>PJ-2023-I</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>ブレイブフロンティア Remaster</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="D69" s="19" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E69" s="19" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="F69" s="19" t="n">
+        <v>308.5</v>
+      </c>
+      <c r="G69" s="19" t="n">
+        <v>171.1</v>
+      </c>
+      <c r="H69" s="19" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="I69" s="19" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="J69" s="19" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="K69" s="19" t="n">
+        <v>709.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>マスターアップ</t>
-        </is>
-      </c>
-      <c r="B70" s="21" t="n">
-        <v>0.9135394862767734</v>
-      </c>
-      <c r="C70" s="21" t="n">
-        <v>0.01808788952320223</v>
-      </c>
-      <c r="D70" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
+          <t>PJ-2024-J</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>オーヴァーロード・サーガ(後半集中)</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="D70" s="19" t="n">
+        <v>153.8</v>
+      </c>
+      <c r="E70" s="19" t="n">
+        <v>254</v>
+      </c>
+      <c r="F70" s="19" t="n">
+        <v>600.1</v>
+      </c>
+      <c r="G70" s="19" t="n">
+        <v>658.4</v>
+      </c>
+      <c r="H70" s="19" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="I70" s="19" t="n">
+        <v>234.8</v>
+      </c>
+      <c r="J70" s="19" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="K70" s="19" t="n">
+        <v>2162.6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr"/>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="19" t="n">
+        <v>1056.6</v>
+      </c>
+      <c r="E71" s="19" t="n">
+        <v>1740.3</v>
+      </c>
+      <c r="F71" s="19" t="n">
+        <v>4009.8</v>
+      </c>
+      <c r="G71" s="19" t="n">
+        <v>4490.2</v>
+      </c>
+      <c r="H71" s="19" t="n">
+        <v>686.6</v>
+      </c>
+      <c r="I71" s="19" t="n">
+        <v>1812.3</v>
+      </c>
+      <c r="J71" s="19" t="n">
+        <v>860.1</v>
+      </c>
+      <c r="K71" s="19" t="n">
+        <v>14655.5</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>■ 行程グループ別 工数比率(学習値)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>件数 = そのグループの形状カーブの学習に参加した案件数。そのグループの業務が無い案件は形の平均に参加しないため、件数が少ないカーブは参考値として扱うこと。比率のほうは業務が無い案件も0として平均に含めている。</t>
-        </is>
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>構成比</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>(全案件の単純合計)</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="17" t="n">
+        <v>0.0721</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>0.1187</v>
+      </c>
+      <c r="F72" s="17" t="n">
+        <v>0.2736</v>
+      </c>
+      <c r="G72" s="17" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="H72" s="17" t="n">
+        <v>0.0468</v>
+      </c>
+      <c r="I72" s="17" t="n">
+        <v>0.1237</v>
+      </c>
+      <c r="J72" s="17" t="n">
+        <v>0.0587</v>
+      </c>
+      <c r="K72" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>行程グループ</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>比率</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>■ マイルストーン位置分布(学習値)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>マイルストーン名</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>平均位置</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>標準偏差</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>企画・プリプロ</t>
-        </is>
-      </c>
-      <c r="B75" s="13" t="n">
-        <v>0.06524885174932314</v>
-      </c>
-      <c r="C75" s="11" t="n">
-        <v>10</v>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>背骨</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>ゲームデザイン・シナリオ</t>
-        </is>
-      </c>
-      <c r="B76" s="13" t="n">
-        <v>0.1122043113713705</v>
-      </c>
-      <c r="C76" s="11" t="n">
-        <v>10</v>
-      </c>
+          <t>プロトタイプ</t>
+        </is>
+      </c>
+      <c r="B76" s="21" t="n">
+        <v>0.2277301327110109</v>
+      </c>
+      <c r="C76" s="21" t="n">
+        <v>0.03189012393515308</v>
+      </c>
+      <c r="D76" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>プログラム</t>
-        </is>
-      </c>
-      <c r="B77" s="13" t="n">
-        <v>0.2879091969215787</v>
-      </c>
-      <c r="C77" s="11" t="n">
+          <t>α版</t>
+        </is>
+      </c>
+      <c r="B77" s="21" t="n">
+        <v>0.4968946897102826</v>
+      </c>
+      <c r="C77" s="21" t="n">
+        <v>0.05787603873596738</v>
+      </c>
+      <c r="D77" s="10" t="n">
         <v>10</v>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>アート</t>
-        </is>
-      </c>
-      <c r="B78" s="13" t="n">
-        <v>0.3005002389104883</v>
-      </c>
-      <c r="C78" s="11" t="n">
+          <t>β版</t>
+        </is>
+      </c>
+      <c r="B78" s="21" t="n">
+        <v>0.7378800534841294</v>
+      </c>
+      <c r="C78" s="21" t="n">
+        <v>0.05000354072467814</v>
+      </c>
+      <c r="D78" s="10" t="n">
         <v>10</v>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
+          <t>マスターアップ</t>
+        </is>
+      </c>
+      <c r="B79" s="21" t="n">
+        <v>0.9135394862767734</v>
+      </c>
+      <c r="C79" s="21" t="n">
+        <v>0.01808788952320223</v>
+      </c>
+      <c r="D79" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>■ 行程グループ別 工数比率(学習値)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>件数 = そのグループの形状カーブの学習に参加した案件数。そのグループの業務が無い案件は形の平均に参加しないため、件数が少ないカーブは参考値として扱うこと。比率のほうは業務が無い案件も0として平均に含めている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>行程グループ</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>比率</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>企画・プリプロ</t>
+        </is>
+      </c>
+      <c r="B84" s="13" t="n">
+        <v>0.06524885174932314</v>
+      </c>
+      <c r="C84" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>ゲームデザイン・シナリオ</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="n">
+        <v>0.1122043113713705</v>
+      </c>
+      <c r="C85" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>プログラム</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="n">
+        <v>0.2879091969215787</v>
+      </c>
+      <c r="C86" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>アート</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="n">
+        <v>0.3005002389104883</v>
+      </c>
+      <c r="C87" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
           <t>サウンド</t>
         </is>
       </c>
-      <c r="B79" s="13" t="n">
+      <c r="B88" s="13" t="n">
         <v>0.04298558319794448</v>
       </c>
-      <c r="C79" s="11" t="n">
+      <c r="C88" s="11" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="10" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>QA・デバッグ</t>
         </is>
       </c>
-      <c r="B80" s="13" t="n">
+      <c r="B89" s="13" t="n">
         <v>0.1327188838365589</v>
       </c>
-      <c r="C80" s="11" t="n">
+      <c r="C89" s="11" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>PM・運営</t>
         </is>
       </c>
-      <c r="B81" s="13" t="n">
+      <c r="B90" s="13" t="n">
         <v>0.05843293401273604</v>
       </c>
-      <c r="C81" s="11" t="n">
+      <c r="C90" s="11" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>■ 警告</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="24" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="24" t="inlineStr">
         <is>
           <t>⚠ マイルストーン「プロトタイプ」はカバー率 5/10 が閾値 60% 未満のため位置合わせには使っていない。</t>
         </is>
